--- a/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.2--20210423105554.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.2--20210423105554.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
